--- a/Sajjad data/by_country_and_state/USA/OK.xlsx
+++ b/Sajjad data/by_country_and_state/USA/OK.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="318">
   <si>
     <t>Business Name</t>
   </si>
@@ -437,6 +437,534 @@
   </si>
   <si>
     <t>2026-10-25T09:48:14.910Z</t>
+  </si>
+  <si>
+    <t>Adventure Vision &amp; Orthodontics</t>
+  </si>
+  <si>
+    <t>(918) 585-3744</t>
+  </si>
+  <si>
+    <t>Orthodontist</t>
+  </si>
+  <si>
+    <t>602 S Utica Ave, Tulsa, OK 74120</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Adventure+Vision+%26+Orthodontics/data=!4m7!3m6!1s0x87b6edbf6ed3f2a9:0x963a8d02c053d4f4!8m2!3d36.1517405!4d-95.9675668!16s%2Fg%2F11y1bwkj3l!19sChIJqfLTbr_ttocR9NRTwAKNOpY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:40:10.515Z</t>
+  </si>
+  <si>
+    <t>Dr. Kerry Edwards</t>
+  </si>
+  <si>
+    <t>(918) 742-9810</t>
+  </si>
+  <si>
+    <t>2930 S Pittsburg Ave, Tulsa, OK 74114</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Kerry+Edwards/data=!4m7!3m6!1s0x87b6ed2d8c8b5fb1:0x41e27f2a639bd403!8m2!3d36.1201247!4d-95.9309732!16s%2Fg%2F1tczfds7!19sChIJsV-LjC3ttocRA9SbYyp_4kE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:40:12.656Z</t>
+  </si>
+  <si>
+    <t>Green Country Orthodontics</t>
+  </si>
+  <si>
+    <t>(918) 932-2708</t>
+  </si>
+  <si>
+    <t>3305 E 45th St suite a, Tulsa, OK 74135</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Green+Country+Orthodontics/data=!4m7!3m6!1s0x87b693ed907029eb:0x1e831b311c3239c8!8m2!3d36.0999201!4d-95.939841!16s%2Fg%2F11h07svf5p!19sChIJ6ylwkO2TtocRyDkyHDEbgx4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:40:27.243Z</t>
+  </si>
+  <si>
+    <t>Emergency Dentist Tulsa TwentyFour Hr</t>
+  </si>
+  <si>
+    <t>(918) 324-4117</t>
+  </si>
+  <si>
+    <t>321 S Boston Ave #300, Tulsa, OK 74103</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dentist+Tulsa+TwentyFour+Hr/data=!4m7!3m6!1s0x87b6eb1e2ae83d69:0xf9d3acb8e8f577e2!8m2!3d36.1532818!4d-95.9891958!16s%2Fg%2F11zzf_151y!19sChIJaT3oKh7rtocR4nf16Lis0_k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:40:57.657Z</t>
+  </si>
+  <si>
+    <t>Dr. Alexander Heifitz Emergency Dentist Tulsa 24/7</t>
+  </si>
+  <si>
+    <t>(918) 539-1600</t>
+  </si>
+  <si>
+    <t>10 E 1st St #22, Tulsa, OK 74103</t>
+  </si>
+  <si>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Alexander+Heifitz+Emergency+Dentist+Tulsa+24%2F7/data=!4m7!3m6!1s0x87b6eb7b56223f57:0xe4aa92b8fac7d5e1!8m2!3d36.154926!4d-95.9915615!16s%2Fg%2F11zf_yzzwb!19sChIJVz8iVnvrtocR4dXH-riSquQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:40:59.684Z</t>
+  </si>
+  <si>
+    <t>Urgent Dental Gateway</t>
+  </si>
+  <si>
+    <t>(918) 739-1652</t>
+  </si>
+  <si>
+    <t>209 N Main St, Tulsa, OK 74103</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Urgent+Dental+Gateway/data=!4m7!3m6!1s0x87b6eb02041fd291:0x31918cc9e341eb70!8m2!3d36.158826!4d-95.9935521!16s%2Fg%2F11p1rfsh0q!19sChIJkdIfBALrtocRcOtB48mMkTE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:41:01.352Z</t>
+  </si>
+  <si>
+    <t>Emergency Dental Now</t>
+  </si>
+  <si>
+    <t>(918) 956-4360</t>
+  </si>
+  <si>
+    <t>601 W Madison St, Broken Arrow, OK 74012</t>
+  </si>
+  <si>
+    <t>Broken Arrow</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dental+Now/data=!4m7!3m6!1s0x87b68b0827e4bdf1:0x4545d48fc25dfe85!8m2!3d36.063639!4d-95.7964314!16s%2Fg%2F11p0wplr34!19sChIJ8b3kJwiLtocRhf5dwo_URUU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:41:03.028Z</t>
+  </si>
+  <si>
+    <t>Dental Path</t>
+  </si>
+  <si>
+    <t>(918) 233-9189</t>
+  </si>
+  <si>
+    <t>9759 E 31st St, Tulsa, OK 74146</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Path/data=!4m7!3m6!1s0x87b68d759665a095:0x356e7f9a47cfc724!8m2!3d36.1190117!4d-95.8660088!16s%2Fg%2F11nvybhm8c!19sChIJlaBllnWNtocRJMfPR5p_bjU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:41:05.487Z</t>
+  </si>
+  <si>
+    <t>Ravishing Smiles &amp; Notary Services</t>
+  </si>
+  <si>
+    <t>(918) 954-3329</t>
+  </si>
+  <si>
+    <t>Teeth whitening service</t>
+  </si>
+  <si>
+    <t>4815 S Harvard Ave #426, Tulsa, OK 74135</t>
+  </si>
+  <si>
+    <t>Open · Closes 6 PM · See more hours</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ravishing+Smiles+%26+Notary+Services/data=!4m7!3m6!1s0x87b69365a4d93ff7:0x18a5b3f9da950e9b!8m2!3d36.0923111!4d-95.9394541!16s%2Fg%2F11q9sfhcgl!19sChIJ9z_ZpGWTtocRmw6V2vmzpRg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:41:42.855Z</t>
+  </si>
+  <si>
+    <t>Dr. Kenneth Ray, D.D.S., M.S</t>
+  </si>
+  <si>
+    <t>(918) 492-7581</t>
+  </si>
+  <si>
+    <t>Dental implants periodontist</t>
+  </si>
+  <si>
+    <t>5010 E 68th St, Tulsa, OK 74136</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>SundayOpen 24 hours; MondayOpen 24 hours; TuesdayOpen 24 hours; WednesdayOpen 24 hours; ThursdayOpen 24 hours; FridayOpen 24 hours; SaturdayOpen 24 hours</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Kenneth+Ray,+D.D.S.,+M.S/data=!4m7!3m6!1s0x87b6925d42b3f483:0xee22a0d35920cccb!8m2!3d36.0641822!4d-95.9205978!16s%2Fg%2F1tgdjhtw!19sChIJg_SzQl2StocRy8wgWdOgIu4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:42:02.199Z</t>
+  </si>
+  <si>
+    <t>Dr. Jerry S. Schoeffler, DDS</t>
+  </si>
+  <si>
+    <t>(918) 492-9711</t>
+  </si>
+  <si>
+    <t>5416 S Yale Ave, Tulsa, OK 74135</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Jerry+S.+Schoeffler,+DDS/data=!4m7!3m6!1s0x87b692ed8ea0c773:0xbc261a46da37b821!8m2!3d36.0850057!4d-95.9233503!16s%2Fg%2F1xb2f2cb!19sChIJc8egju2StocRIbg32kYaJrw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:42:05.138Z</t>
+  </si>
+  <si>
+    <t>Dr. Ted L. Marshall, DMD</t>
+  </si>
+  <si>
+    <t>(918) 492-6200</t>
+  </si>
+  <si>
+    <t>8830 S Yale Ave, Tulsa, OK 74137</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Ted+L.+Marshall,+DMD/data=!4m7!3m6!1s0x87b69221a75817c7:0x46dfcce01bababb4!8m2!3d36.034823!4d-95.9208708!16s%2Fg%2F1thks69r!19sChIJxxdYpyGStocRtKurG-DM30Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:42:06.909Z</t>
+  </si>
+  <si>
+    <t>Parker Jeff K DDS</t>
+  </si>
+  <si>
+    <t>(918) 744-6080</t>
+  </si>
+  <si>
+    <t>1508 S Denver Ave., Tulsa, OK 74119</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Parker+Jeff+K+DDS/data=!4m7!3m6!1s0x87b6eb660afd8d21:0xa53bedb2c052faf4!8m2!3d36.140371!4d-95.992651!16s%2Fg%2F1tkb5mds!19sChIJIY39CmbrtocR9PpSwLLtO6U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:42:09.303Z</t>
+  </si>
+  <si>
+    <t>Bennett Jill a DDS</t>
+  </si>
+  <si>
+    <t>(918) 493-1865</t>
+  </si>
+  <si>
+    <t>4606 E 67th St Suite 310, Tulsa, OK 74136</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bennett+Jill+a+DDS/data=!4m7!3m6!1s0x87b6925bf08c39d5:0x3fa14c3216b6eda8!8m2!3d36.0671652!4d-95.9246182!16s%2Fg%2F1tfwqg_9!19sChIJ1TmM8FuStocRqO22FjJMoT8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:42:11.308Z</t>
+  </si>
+  <si>
+    <t>Hall Scott DDS</t>
+  </si>
+  <si>
+    <t>(918) 495-0700</t>
+  </si>
+  <si>
+    <t>Periodontist</t>
+  </si>
+  <si>
+    <t>6465 S Yale Ave #607, Tulsa, OK 74136</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hall+Scott+DDS/data=!4m7!3m6!1s0x87b6925e31c6794f:0xbc7cc808ea92349b!8m2!3d36.0704751!4d-95.9203639!16s%2Fg%2F1tfb2hx3!19sChIJT3nGMV6StocRmzSS6gjIfLw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:42:15.273Z</t>
+  </si>
+  <si>
+    <t>Stanley S Groom DDS</t>
+  </si>
+  <si>
+    <t>(918) 628-0311</t>
+  </si>
+  <si>
+    <t>5801 E 41st St #900, Tulsa, OK 74135</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Stanley+S+Groom+DDS/data=!4m7!3m6!1s0x87b692baefe31e79:0x6bda8f547e67dc72!8m2!3d36.1049787!4d-95.9111995!16s%2Fg%2F1thpxbpv!19sChIJeR7j77qStocRctxnflSP2ms?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:42:17.234Z</t>
+  </si>
+  <si>
+    <t>Dr. Randall E. Venk, DDS</t>
+  </si>
+  <si>
+    <t>(405) 321-6506</t>
+  </si>
+  <si>
+    <t>709 W Main St, Norman, OK 73069</t>
+  </si>
+  <si>
+    <t>Norman</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Randall+E.+Venk,+DDS/data=!4m7!3m6!1s0x87b269c5ca303e45:0x86e7b34d3bda634e!8m2!3d35.2187837!4d-97.4537017!16s%2Fg%2F1tsyq8yg!19sChIJRT4wysVpsocRTmPaO02z54Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:43:23.089Z</t>
+  </si>
+  <si>
+    <t>Norman Endodontics</t>
+  </si>
+  <si>
+    <t>(405) 307-8200</t>
+  </si>
+  <si>
+    <t>Endodontist</t>
+  </si>
+  <si>
+    <t>3321 W Rock Creek Rd Ste 130, Norman, OK 73072</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Norman+Endodontics/data=!4m7!3m6!1s0x87b26bda85eca7b9:0xde489d2aaa0c0e3b!8m2!3d35.2482757!4d-97.4907684!16s%2Fg%2F11n6rsp8y_!19sChIJuafshdprsocROw4MqiqdSN4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:43:53.371Z</t>
+  </si>
+  <si>
+    <t>Dr. Morolayo Oluyemi Emergency Dental Service</t>
+  </si>
+  <si>
+    <t>(405) 507-9100</t>
+  </si>
+  <si>
+    <t>202 N Porter Ave, Norman, OK 73071</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Morolayo+Oluyemi+Emergency+Dental+Service/data=!4m7!3m6!1s0x87b269ddc52aae9f:0xa54515aa18c887e8!8m2!3d35.223743!4d-97.440155!16s%2Fg%2F11zx13sh4z!19sChIJn64qxd1psocR6IfIGKoVRaU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:43:59.350Z</t>
+  </si>
+  <si>
+    <t>Griffith Dentistry</t>
+  </si>
+  <si>
+    <t>(405) 364-8550</t>
+  </si>
+  <si>
+    <t>3924 W Tecumseh Rd, Norman, OK 73072</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Griffith+Dentistry/data=!4m7!3m6!1s0x87b26b002c448505:0x3d0e5d7bae85121d!8m2!3d35.2614062!4d-97.4988742!16s%2Fg%2F11vyj5jkwt!19sChIJBYVELABrsocRHRKFrntdDj0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:44:19.483Z</t>
+  </si>
+  <si>
+    <t>Dr. James Yeary</t>
+  </si>
+  <si>
+    <t>(405) 329-7171</t>
+  </si>
+  <si>
+    <t>801 Wall St, Norman, OK 73069</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+James+Yeary/data=!4m7!3m6!1s0x87b2699fd4453279:0x4ae3bb18cda1eac4!8m2!3d35.2276825!4d-97.481197!16s%2Fg%2F11t5bczbs0!19sChIJeTJF1J9psocRxOqhzRi740o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:44:50.668Z</t>
+  </si>
+  <si>
+    <t>Gentle Family Dentistry: Nabors Donna</t>
+  </si>
+  <si>
+    <t>(405) 321-4060</t>
+  </si>
+  <si>
+    <t>509 S Porter Ave, Norman, OK 73071</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Gentle+Family+Dentistry:+Nabors+Donna/data=!4m7!3m6!1s0x87b24277b96d531b:0xd2aa8a84e1088904!8m2!3d35.2188502!4d-97.4364256!16s%2Fg%2F1vbl82lz!19sChIJG1NtuXdCsocRBIkI4YSKqtI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:44:53.477Z</t>
+  </si>
+  <si>
+    <t>Ryan A Streight DDS</t>
+  </si>
+  <si>
+    <t>(405) 321-1926</t>
+  </si>
+  <si>
+    <t>706 24th Ave NW, Norman, OK 73069</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ryan+A+Streight+DDS/data=!4m7!3m6!1s0x87b2699f076acc05:0x6defd05c89bab578!8m2!3d35.2272376!4d-97.478749!16s%2Fg%2F1ptvvbyym!19sChIJBcxqB59psocReLW6iVzQ720?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:45:18.370Z</t>
+  </si>
+  <si>
+    <t>Arrow Springs Dental Care</t>
+  </si>
+  <si>
+    <t>(918) 451-9066</t>
+  </si>
+  <si>
+    <t>3764 S Elm Pl, Broken Arrow, OK 74011</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Arrow+Springs+Dental+Care/data=!4m7!3m6!1s0x87b68940bec64575:0x3d02bd4101d88961!8m2!3d36.0147991!4d-95.7974502!16s%2Fg%2F11b7jgh402!19sChIJdUXGvkCJtocRYYnYAUG9Aj0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:46:58.544Z</t>
+  </si>
+  <si>
+    <t>Aspen Medical Center</t>
+  </si>
+  <si>
+    <t>(918) 451-0211</t>
+  </si>
+  <si>
+    <t>3300 S Aspen Ave # A, Broken Arrow, OK 74012</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Aspen+Medical+Center/data=!4m7!3m6!1s0x87b68eb3610c7371:0x340c76aa94ebc51e!8m2!3d36.0194119!4d-95.8159415!16s%2Fg%2F1th0ndvx!19sChIJcXMMYbOOtocRHsXrlKp2DDQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:47:00.929Z</t>
+  </si>
+  <si>
+    <t>Dr. Bradford D. Overton, DDS</t>
+  </si>
+  <si>
+    <t>(918) 258-2323</t>
+  </si>
+  <si>
+    <t>817 S Elm Pl, Broken Arrow, OK 74012</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Bradford+D.+Overton,+DDS/data=!4m7!3m6!1s0x87b68be6f3be2185:0x6f21f0543d47ab74!8m2!3d36.044112!4d-95.796922!16s%2Fg%2F1tcvpsnm!19sChIJhSG-8-aLtocRdKtHPVTwIW8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:48:54.091Z</t>
+  </si>
+  <si>
+    <t>R2 Center for Dentistry</t>
+  </si>
+  <si>
+    <t>(918) 455-0811</t>
+  </si>
+  <si>
+    <t>2619 S Elm Pl, Broken Arrow, OK 74012</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/R2+Center+for+Dentistry/data=!4m7!3m6!1s0x87b6898707816cbb:0x471aba891a14c48b!8m2!3d36.0257694!4d-95.7969858!16s%2Fg%2F11mbww46_2!19sChIJu2yBB4eJtocRi8QUGom6Gkc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:49:12.767Z</t>
+  </si>
+  <si>
+    <t>Dr. Steven W. Hogg, DDS</t>
+  </si>
+  <si>
+    <t>(918) 455-8899</t>
+  </si>
+  <si>
+    <t>423 West Washington St S, Broken Arrow, OK 74012</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Steven+W.+Hogg,+DDS/data=!4m7!3m6!1s0x87b6895e635fbc19:0xb5a58747f87d8941!8m2!3d36.031514!4d-95.7955048!16s%2Fg%2F1tk8cmpp!19sChIJGbxfY16JtocRQYl9-EeHpbU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:49:14.797Z</t>
+  </si>
+  <si>
+    <t>Dr. Michael Wallace</t>
+  </si>
+  <si>
+    <t>(405) 340-0411</t>
+  </si>
+  <si>
+    <t>1617 E Danforth Rd Ste A, Edmond, OK 73034</t>
+  </si>
+  <si>
+    <t>Edmond</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Michael+Wallace/data=!4m7!3m6!1s0x87b21fea21900001:0x6452c156de0787a2!8m2!3d35.6676511!4d-97.4582932!16s%2Fg%2F11qgb73hm4!19sChIJAQCQIeofsocRoocH3lbBUmQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:51:32.471Z</t>
+  </si>
+  <si>
+    <t>Dr. Daniel J. Wilguess, DDS</t>
+  </si>
+  <si>
+    <t>(405) 341-6134</t>
+  </si>
+  <si>
+    <t>233 E 10th Street Plaza, Edmond, OK 73034</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Daniel+J.+Wilguess,+DDS/data=!4m7!3m6!1s0x87b3d8f4ff6bba61:0x95f0a4fa7cd8f9d9!8m2!3d35.6425943!4d-97.4763128!16s%2Fg%2F1vzqss55!19sChIJYbpr__TYs4cR2fnYfPqk8JU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:51:34.531Z</t>
+  </si>
+  <si>
+    <t>Fillmore Catherine E DDS</t>
+  </si>
+  <si>
+    <t>(570) 286-7500</t>
+  </si>
+  <si>
+    <t>17900 N Western Ave #104, Edmond, OK 73012</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Fillmore+Catherine+E+DDS/data=!4m7!3m6!1s0x87b21ddc16fcfb39:0xf6f5e4d5e6474678!8m2!3d35.6538378!4d-97.5312668!16s%2Fg%2F1263zps45!19sChIJOfv8FtwdsocReEZH5tXk9fY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:52:14.041Z</t>
+  </si>
+  <si>
+    <t>Dr. Eli T. Jarjoura, DDS</t>
+  </si>
+  <si>
+    <t>(405) 844-8887</t>
+  </si>
+  <si>
+    <t>3225 Teakwood Ln, Edmond, OK 73013</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Eli+T.+Jarjoura,+DDS/data=!4m7!3m6!1s0x87b21f1f00000001:0xc64189b324868761!8m2!3d35.6238917!4d-97.4944852!16s%2Fg%2F11h6npk8vd!19sChIJAQAAAB8fsocRYYeGJLOJQcY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:53:02.796Z</t>
   </si>
 </sst>
 </file>
@@ -817,7 +1345,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1736,6 +2264,1318 @@
         <v>141</v>
       </c>
     </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>142</v>
+      </c>
+      <c r="B23" t="s">
+        <v>143</v>
+      </c>
+      <c r="C23" t="s">
+        <v>144</v>
+      </c>
+      <c r="D23" t="s">
+        <v>145</v>
+      </c>
+      <c r="E23" t="s">
+        <v>113</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s">
+        <v>146</v>
+      </c>
+      <c r="I23" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" t="s">
+        <v>147</v>
+      </c>
+      <c r="M23" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>149</v>
+      </c>
+      <c r="B24" t="s">
+        <v>150</v>
+      </c>
+      <c r="C24" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" t="s">
+        <v>151</v>
+      </c>
+      <c r="E24" t="s">
+        <v>113</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" t="s">
+        <v>31</v>
+      </c>
+      <c r="J24" t="s">
+        <v>44</v>
+      </c>
+      <c r="K24" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" t="s">
+        <v>152</v>
+      </c>
+      <c r="M24" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>154</v>
+      </c>
+      <c r="B25" t="s">
+        <v>155</v>
+      </c>
+      <c r="C25" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" t="s">
+        <v>156</v>
+      </c>
+      <c r="E25" t="s">
+        <v>113</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s">
+        <v>43</v>
+      </c>
+      <c r="I25" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s">
+        <v>30</v>
+      </c>
+      <c r="K25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" t="s">
+        <v>157</v>
+      </c>
+      <c r="M25" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>159</v>
+      </c>
+      <c r="B26" t="s">
+        <v>160</v>
+      </c>
+      <c r="C26" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" t="s">
+        <v>161</v>
+      </c>
+      <c r="E26" t="s">
+        <v>113</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s">
+        <v>43</v>
+      </c>
+      <c r="I26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" t="s">
+        <v>162</v>
+      </c>
+      <c r="M26" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>164</v>
+      </c>
+      <c r="B27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" t="s">
+        <v>166</v>
+      </c>
+      <c r="E27" t="s">
+        <v>113</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s">
+        <v>167</v>
+      </c>
+      <c r="I27" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" t="s">
+        <v>22</v>
+      </c>
+      <c r="K27" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" t="s">
+        <v>168</v>
+      </c>
+      <c r="M27" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>170</v>
+      </c>
+      <c r="B28" t="s">
+        <v>171</v>
+      </c>
+      <c r="C28" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" t="s">
+        <v>172</v>
+      </c>
+      <c r="E28" t="s">
+        <v>113</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s">
+        <v>30</v>
+      </c>
+      <c r="I28" t="s">
+        <v>31</v>
+      </c>
+      <c r="J28" t="s">
+        <v>30</v>
+      </c>
+      <c r="K28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" t="s">
+        <v>173</v>
+      </c>
+      <c r="M28" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>175</v>
+      </c>
+      <c r="B29" t="s">
+        <v>176</v>
+      </c>
+      <c r="C29" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" t="s">
+        <v>177</v>
+      </c>
+      <c r="E29" t="s">
+        <v>178</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s">
+        <v>43</v>
+      </c>
+      <c r="I29" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" t="s">
+        <v>30</v>
+      </c>
+      <c r="K29" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" t="s">
+        <v>179</v>
+      </c>
+      <c r="M29" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>181</v>
+      </c>
+      <c r="B30" t="s">
+        <v>182</v>
+      </c>
+      <c r="C30" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" t="s">
+        <v>183</v>
+      </c>
+      <c r="E30" t="s">
+        <v>113</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s">
+        <v>30</v>
+      </c>
+      <c r="I30" t="s">
+        <v>31</v>
+      </c>
+      <c r="J30" t="s">
+        <v>30</v>
+      </c>
+      <c r="K30" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" t="s">
+        <v>184</v>
+      </c>
+      <c r="M30" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>186</v>
+      </c>
+      <c r="B31" t="s">
+        <v>187</v>
+      </c>
+      <c r="C31" t="s">
+        <v>188</v>
+      </c>
+      <c r="D31" t="s">
+        <v>189</v>
+      </c>
+      <c r="E31" t="s">
+        <v>113</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s">
+        <v>43</v>
+      </c>
+      <c r="I31" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" t="s">
+        <v>190</v>
+      </c>
+      <c r="K31" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" t="s">
+        <v>191</v>
+      </c>
+      <c r="M31" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>193</v>
+      </c>
+      <c r="B32" t="s">
+        <v>194</v>
+      </c>
+      <c r="C32" t="s">
+        <v>195</v>
+      </c>
+      <c r="D32" t="s">
+        <v>196</v>
+      </c>
+      <c r="E32" t="s">
+        <v>113</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s">
+        <v>197</v>
+      </c>
+      <c r="I32" t="s">
+        <v>198</v>
+      </c>
+      <c r="J32" t="s">
+        <v>199</v>
+      </c>
+      <c r="K32" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" t="s">
+        <v>200</v>
+      </c>
+      <c r="M32" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>202</v>
+      </c>
+      <c r="B33" t="s">
+        <v>203</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" t="s">
+        <v>204</v>
+      </c>
+      <c r="E33" t="s">
+        <v>113</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s">
+        <v>43</v>
+      </c>
+      <c r="I33" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" t="s">
+        <v>44</v>
+      </c>
+      <c r="K33" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" t="s">
+        <v>205</v>
+      </c>
+      <c r="M33" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>207</v>
+      </c>
+      <c r="B34" t="s">
+        <v>208</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" t="s">
+        <v>209</v>
+      </c>
+      <c r="E34" t="s">
+        <v>113</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s">
+        <v>50</v>
+      </c>
+      <c r="I34" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" t="s">
+        <v>44</v>
+      </c>
+      <c r="K34" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" t="s">
+        <v>210</v>
+      </c>
+      <c r="M34" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>212</v>
+      </c>
+      <c r="B35" t="s">
+        <v>213</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" t="s">
+        <v>214</v>
+      </c>
+      <c r="E35" t="s">
+        <v>113</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s">
+        <v>50</v>
+      </c>
+      <c r="I35" t="s">
+        <v>21</v>
+      </c>
+      <c r="J35" t="s">
+        <v>30</v>
+      </c>
+      <c r="K35" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" t="s">
+        <v>215</v>
+      </c>
+      <c r="M35" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>217</v>
+      </c>
+      <c r="B36" t="s">
+        <v>218</v>
+      </c>
+      <c r="C36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E36" t="s">
+        <v>113</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s">
+        <v>43</v>
+      </c>
+      <c r="I36" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s">
+        <v>30</v>
+      </c>
+      <c r="K36" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" t="s">
+        <v>220</v>
+      </c>
+      <c r="M36" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>222</v>
+      </c>
+      <c r="B37" t="s">
+        <v>223</v>
+      </c>
+      <c r="C37" t="s">
+        <v>224</v>
+      </c>
+      <c r="D37" t="s">
+        <v>225</v>
+      </c>
+      <c r="E37" t="s">
+        <v>113</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s">
+        <v>30</v>
+      </c>
+      <c r="I37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J37" t="s">
+        <v>44</v>
+      </c>
+      <c r="K37" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" t="s">
+        <v>226</v>
+      </c>
+      <c r="M37" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>228</v>
+      </c>
+      <c r="B38" t="s">
+        <v>229</v>
+      </c>
+      <c r="C38" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" t="s">
+        <v>230</v>
+      </c>
+      <c r="E38" t="s">
+        <v>113</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" t="s">
+        <v>43</v>
+      </c>
+      <c r="I38" t="s">
+        <v>21</v>
+      </c>
+      <c r="J38" t="s">
+        <v>44</v>
+      </c>
+      <c r="K38" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" t="s">
+        <v>231</v>
+      </c>
+      <c r="M38" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>233</v>
+      </c>
+      <c r="B39" t="s">
+        <v>234</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>235</v>
+      </c>
+      <c r="E39" t="s">
+        <v>236</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" t="s">
+        <v>50</v>
+      </c>
+      <c r="I39" t="s">
+        <v>21</v>
+      </c>
+      <c r="J39" t="s">
+        <v>44</v>
+      </c>
+      <c r="K39" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" t="s">
+        <v>237</v>
+      </c>
+      <c r="M39" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>239</v>
+      </c>
+      <c r="B40" t="s">
+        <v>240</v>
+      </c>
+      <c r="C40" t="s">
+        <v>241</v>
+      </c>
+      <c r="D40" t="s">
+        <v>242</v>
+      </c>
+      <c r="E40" t="s">
+        <v>236</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" t="s">
+        <v>67</v>
+      </c>
+      <c r="I40" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" t="s">
+        <v>44</v>
+      </c>
+      <c r="K40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" t="s">
+        <v>243</v>
+      </c>
+      <c r="M40" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>245</v>
+      </c>
+      <c r="B41" t="s">
+        <v>246</v>
+      </c>
+      <c r="C41" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" t="s">
+        <v>247</v>
+      </c>
+      <c r="E41" t="s">
+        <v>236</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I41" t="s">
+        <v>31</v>
+      </c>
+      <c r="J41" t="s">
+        <v>30</v>
+      </c>
+      <c r="K41" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" t="s">
+        <v>248</v>
+      </c>
+      <c r="M41" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>250</v>
+      </c>
+      <c r="B42" t="s">
+        <v>251</v>
+      </c>
+      <c r="C42" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" t="s">
+        <v>252</v>
+      </c>
+      <c r="E42" t="s">
+        <v>236</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" t="s">
+        <v>43</v>
+      </c>
+      <c r="I42" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s">
+        <v>44</v>
+      </c>
+      <c r="K42" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" t="s">
+        <v>253</v>
+      </c>
+      <c r="M42" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>255</v>
+      </c>
+      <c r="B43" t="s">
+        <v>256</v>
+      </c>
+      <c r="C43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" t="s">
+        <v>257</v>
+      </c>
+      <c r="E43" t="s">
+        <v>236</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" t="s">
+        <v>258</v>
+      </c>
+      <c r="I43" t="s">
+        <v>21</v>
+      </c>
+      <c r="J43" t="s">
+        <v>30</v>
+      </c>
+      <c r="K43" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" t="s">
+        <v>259</v>
+      </c>
+      <c r="M43" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>261</v>
+      </c>
+      <c r="B44" t="s">
+        <v>262</v>
+      </c>
+      <c r="C44" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" t="s">
+        <v>263</v>
+      </c>
+      <c r="E44" t="s">
+        <v>236</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" t="s">
+        <v>30</v>
+      </c>
+      <c r="I44" t="s">
+        <v>31</v>
+      </c>
+      <c r="J44" t="s">
+        <v>30</v>
+      </c>
+      <c r="K44" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" t="s">
+        <v>264</v>
+      </c>
+      <c r="M44" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>266</v>
+      </c>
+      <c r="B45" t="s">
+        <v>267</v>
+      </c>
+      <c r="C45" t="s">
+        <v>144</v>
+      </c>
+      <c r="D45" t="s">
+        <v>268</v>
+      </c>
+      <c r="E45" t="s">
+        <v>236</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" t="s">
+        <v>43</v>
+      </c>
+      <c r="I45" t="s">
+        <v>21</v>
+      </c>
+      <c r="J45" t="s">
+        <v>30</v>
+      </c>
+      <c r="K45" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" t="s">
+        <v>269</v>
+      </c>
+      <c r="M45" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>271</v>
+      </c>
+      <c r="B46" t="s">
+        <v>272</v>
+      </c>
+      <c r="C46" t="s">
+        <v>28</v>
+      </c>
+      <c r="D46" t="s">
+        <v>273</v>
+      </c>
+      <c r="E46" t="s">
+        <v>178</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" t="s">
+        <v>43</v>
+      </c>
+      <c r="I46" t="s">
+        <v>21</v>
+      </c>
+      <c r="J46" t="s">
+        <v>44</v>
+      </c>
+      <c r="K46" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" t="s">
+        <v>274</v>
+      </c>
+      <c r="M46" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>276</v>
+      </c>
+      <c r="B47" t="s">
+        <v>277</v>
+      </c>
+      <c r="C47" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" t="s">
+        <v>278</v>
+      </c>
+      <c r="E47" t="s">
+        <v>178</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" t="s">
+        <v>43</v>
+      </c>
+      <c r="I47" t="s">
+        <v>21</v>
+      </c>
+      <c r="J47" t="s">
+        <v>44</v>
+      </c>
+      <c r="K47" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" t="s">
+        <v>279</v>
+      </c>
+      <c r="M47" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>281</v>
+      </c>
+      <c r="B48" t="s">
+        <v>282</v>
+      </c>
+      <c r="C48" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" t="s">
+        <v>283</v>
+      </c>
+      <c r="E48" t="s">
+        <v>178</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" t="s">
+        <v>67</v>
+      </c>
+      <c r="I48" t="s">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s">
+        <v>44</v>
+      </c>
+      <c r="K48" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" t="s">
+        <v>284</v>
+      </c>
+      <c r="M48" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>286</v>
+      </c>
+      <c r="B49" t="s">
+        <v>287</v>
+      </c>
+      <c r="C49" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" t="s">
+        <v>288</v>
+      </c>
+      <c r="E49" t="s">
+        <v>178</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" t="s">
+        <v>289</v>
+      </c>
+      <c r="I49" t="s">
+        <v>21</v>
+      </c>
+      <c r="J49" t="s">
+        <v>44</v>
+      </c>
+      <c r="K49" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" t="s">
+        <v>290</v>
+      </c>
+      <c r="M49" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>292</v>
+      </c>
+      <c r="B50" t="s">
+        <v>293</v>
+      </c>
+      <c r="C50" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" t="s">
+        <v>294</v>
+      </c>
+      <c r="E50" t="s">
+        <v>178</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" t="s">
+        <v>79</v>
+      </c>
+      <c r="I50" t="s">
+        <v>21</v>
+      </c>
+      <c r="J50" t="s">
+        <v>44</v>
+      </c>
+      <c r="K50" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" t="s">
+        <v>295</v>
+      </c>
+      <c r="M50" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>297</v>
+      </c>
+      <c r="B51" t="s">
+        <v>298</v>
+      </c>
+      <c r="C51" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" t="s">
+        <v>299</v>
+      </c>
+      <c r="E51" t="s">
+        <v>300</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" t="s">
+        <v>289</v>
+      </c>
+      <c r="I51" t="s">
+        <v>21</v>
+      </c>
+      <c r="J51" t="s">
+        <v>30</v>
+      </c>
+      <c r="K51" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" t="s">
+        <v>301</v>
+      </c>
+      <c r="M51" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>303</v>
+      </c>
+      <c r="B52" t="s">
+        <v>304</v>
+      </c>
+      <c r="C52" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" t="s">
+        <v>305</v>
+      </c>
+      <c r="E52" t="s">
+        <v>300</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52" t="s">
+        <v>61</v>
+      </c>
+      <c r="I52" t="s">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s">
+        <v>44</v>
+      </c>
+      <c r="K52" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" t="s">
+        <v>306</v>
+      </c>
+      <c r="M52" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>308</v>
+      </c>
+      <c r="B53" t="s">
+        <v>309</v>
+      </c>
+      <c r="C53" t="s">
+        <v>77</v>
+      </c>
+      <c r="D53" t="s">
+        <v>310</v>
+      </c>
+      <c r="E53" t="s">
+        <v>300</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" t="s">
+        <v>30</v>
+      </c>
+      <c r="I53" t="s">
+        <v>31</v>
+      </c>
+      <c r="J53" t="s">
+        <v>30</v>
+      </c>
+      <c r="K53" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" t="s">
+        <v>311</v>
+      </c>
+      <c r="M53" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>313</v>
+      </c>
+      <c r="B54" t="s">
+        <v>314</v>
+      </c>
+      <c r="C54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" t="s">
+        <v>315</v>
+      </c>
+      <c r="E54" t="s">
+        <v>300</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" t="s">
+        <v>20</v>
+      </c>
+      <c r="I54" t="s">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s">
+        <v>30</v>
+      </c>
+      <c r="K54" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" t="s">
+        <v>316</v>
+      </c>
+      <c r="M54" t="s">
+        <v>317</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
